--- a/data/trans_camb/IP16A03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 12,39</t>
+          <t>-8,67; 12,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 14,98</t>
+          <t>-11,24; 13,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 0,0</t>
+          <t>-17,14; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 7,35</t>
+          <t>-13,88; 7,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 35,47</t>
+          <t>-10,29; 34,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 31,74</t>
+          <t>-7,62; 33,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 6,33</t>
+          <t>-8,91; 6,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 16,3</t>
+          <t>-7,73; 15,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 14,48</t>
+          <t>-9,0; 15,83</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 337,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 897,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 3,58</t>
+          <t>-7,8; 3,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -1,19</t>
+          <t>-10,06; -1,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 0,54</t>
+          <t>-8,96; 0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 1,95</t>
+          <t>-9,59; 2,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -0,96</t>
+          <t>-10,86; -0,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 0,72</t>
+          <t>-9,86; 0,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,19</t>
+          <t>-6,59; 0,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -1,92</t>
+          <t>-8,53; -2,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -0,31</t>
+          <t>-7,74; -0,67</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,45; 157,04</t>
+          <t>-83,01; 105,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -1,13</t>
+          <t>-100,0; 39,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,46</t>
+          <t>-100,0; 27,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-91,33; 68,01</t>
+          <t>-88,66; 99,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,9</t>
+          <t>-100,0; -0,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,95; 36,6</t>
+          <t>-85,13; 47,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-78,21; 35,27</t>
+          <t>-74,16; 22,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,76; -30,52</t>
+          <t>-94,44; -34,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-83,12; -1,59</t>
+          <t>-83,46; -9,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 6,15</t>
+          <t>-11,56; 5,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 4,68</t>
+          <t>-13,51; 4,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 0,48</t>
+          <t>-15,62; 1,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 5,52</t>
+          <t>-13,24; 5,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 19,55</t>
+          <t>-6,76; 17,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,24; -2,06</t>
+          <t>-19,55; -2,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 3,28</t>
+          <t>-9,65; 3,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 9,48</t>
+          <t>-7,83; 8,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,06; -2,15</t>
+          <t>-14,51; -2,03</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 396,04</t>
+          <t>-100,0; 370,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,97; 635,53</t>
+          <t>-62,4; 714,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,5; 140,22</t>
+          <t>-85,82; 156,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,25; 369,44</t>
+          <t>-69,56; 286,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; -10,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 2,86</t>
+          <t>-5,49; 3,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -0,57</t>
+          <t>-7,97; -0,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -0,99</t>
+          <t>-8,24; -0,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 0,78</t>
+          <t>-7,73; 1,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 2,14</t>
+          <t>-6,88; 2,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 0,03</t>
+          <t>-8,33; -0,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 0,18</t>
+          <t>-5,51; 0,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,26</t>
+          <t>-6,29; -0,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; -1,21</t>
+          <t>-7,36; -1,76</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 90,41</t>
+          <t>-68,85; 107,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-93,58; -1,78</t>
+          <t>-92,15; 0,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-94,44; -0,94</t>
+          <t>-93,67; -9,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,6; 27,71</t>
+          <t>-79,98; 35,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 53,09</t>
+          <t>-72,41; 55,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,56; 8,13</t>
+          <t>-82,27; 7,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,66; 5,89</t>
+          <t>-67,44; 9,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,52; -3,41</t>
+          <t>-73,73; -1,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,62; -20,25</t>
+          <t>-82,24; -29,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 12,49</t>
+          <t>-8,53; 12,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 13,93</t>
+          <t>-11,32; 14,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 0,0</t>
+          <t>-17,11; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 7,27</t>
+          <t>-13,64; 7,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 34,53</t>
+          <t>-10,3; 35,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 33,12</t>
+          <t>-7,53; 29,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 6,92</t>
+          <t>-7,83; 8,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 15,35</t>
+          <t>-7,92; 13,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 15,83</t>
+          <t>-7,85; 13,49</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 563,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 3,11</t>
+          <t>-7,52; 3,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -1,25</t>
+          <t>-10,43; -1,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 0,37</t>
+          <t>-9,01; 0,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 2,25</t>
+          <t>-9,52; 2,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -0,94</t>
+          <t>-10,8; -1,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 0,84</t>
+          <t>-9,3; 1,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 0,79</t>
+          <t>-6,92; 1,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -2,07</t>
+          <t>-8,96; -2,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -0,67</t>
+          <t>-7,56; -0,6</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,01; 105,27</t>
+          <t>-81,51; 134,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,9</t>
+          <t>-100,0; -4,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,22</t>
+          <t>-100,0; 42,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,66; 99,44</t>
+          <t>-89,52; 111,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,34</t>
+          <t>-100,0; 12,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,13; 47,19</t>
+          <t>-83,94; 44,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,16; 22,05</t>
+          <t>-75,2; 28,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,44; -34,0</t>
+          <t>-94,72; -29,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-83,46; -9,89</t>
+          <t>-84,74; -9,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 5,99</t>
+          <t>-13,14; 5,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 4,72</t>
+          <t>-13,69; 4,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 1,01</t>
+          <t>-16,53; 1,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 5,54</t>
+          <t>-13,0; 5,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 17,71</t>
+          <t>-6,44; 17,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,55; -2,09</t>
+          <t>-19,44; -2,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 3,62</t>
+          <t>-10,23; 3,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 8,75</t>
+          <t>-6,96; 8,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -2,03</t>
+          <t>-13,81; -2,38</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 370,64</t>
+          <t>-100,0; 612,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,4; 714,03</t>
+          <t>-58,19; 617,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,82; 156,02</t>
+          <t>-86,79; 140,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 286,47</t>
+          <t>-71,64; 290,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -10,79</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,27</t>
+          <t>-5,67; 3,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -0,52</t>
+          <t>-8,09; -0,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -0,79</t>
+          <t>-8,55; -1,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 1,16</t>
+          <t>-8,06; 0,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 2,44</t>
+          <t>-7,19; 2,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,33; -0,05</t>
+          <t>-8,27; -0,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,33</t>
+          <t>-5,59; 0,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,29; -0,43</t>
+          <t>-6,23; -0,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,36; -1,76</t>
+          <t>-7,02; -1,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,85; 107,12</t>
+          <t>-68,07; 96,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-92,15; 0,77</t>
+          <t>-94,06; -2,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-93,67; -9,51</t>
+          <t>-93,9; -11,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-79,98; 35,44</t>
+          <t>-78,84; 33,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,41; 55,21</t>
+          <t>-73,23; 62,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,27; 7,19</t>
+          <t>-79,52; 4,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-67,44; 9,26</t>
+          <t>-67,81; 10,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,73; -1,64</t>
+          <t>-74,73; -3,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,24; -29,29</t>
+          <t>-82,46; -25,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A03-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,52</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,63</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,77</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-5,65</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,01</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-1,16</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>-0,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 12,51</t>
+          <t>-13,72; 7,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 14,81</t>
+          <t>-10,18; 35,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 0,0</t>
+          <t>-10,18; 22,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 7,26</t>
+          <t>-10,2; 12,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 35,39</t>
+          <t>-11,24; 14,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 29,33</t>
+          <t>-17,52; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 8,09</t>
+          <t>-9,34; 6,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 13,92</t>
+          <t>-7,66; 16,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 13,49</t>
+          <t>-8,55; 11,93</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-47,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53,09%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39,68%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>8,21%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-13,63%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-47,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>53,09%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>90,63%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-18,96%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>-11,1%</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 563,25</t>
+          <t>-100,0; 337,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 897,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-3,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-5,47</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,52</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,89</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,94</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,47</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,7</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,84</t>
+          <t>-3,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 3,32</t>
+          <t>-9,83; 1,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,43; -1,42</t>
+          <t>-11,22; -0,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 0,35</t>
+          <t>-10,05; 1,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 2,07</t>
+          <t>-7,13; 3,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -1,1</t>
+          <t>-10,26; -1,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 1,14</t>
+          <t>-8,46; 0,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 1,07</t>
+          <t>-6,68; 1,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -2,01</t>
+          <t>-8,86; -1,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -0,6</t>
+          <t>-7,05; -0,0</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-51,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-76,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-49,46%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-29,19%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-81,69%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-65,79%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-51,31%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-76,85%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-51,96%</t>
+          <t>-59,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-58,46%</t>
+          <t>-53,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,51; 134,78</t>
+          <t>-91,33; 68,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,08</t>
+          <t>-100,0; 13,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,72</t>
+          <t>-85,0; 42,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-89,52; 111,38</t>
+          <t>-81,45; 157,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,52</t>
+          <t>-100,0; -1,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,94; 44,28</t>
+          <t>-91,73; 82,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,2; 28,64</t>
+          <t>-78,21; 35,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,72; -29,8</t>
+          <t>-94,76; -30,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-84,74; -9,3</t>
+          <t>-79,75; 9,06</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,36</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-8,18</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,87</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,31</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,2</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,36</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-8,18</t>
+          <t>-4,42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,59</t>
+          <t>-6,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 5,87</t>
+          <t>-14,23; 5,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 4,67</t>
+          <t>-5,46; 19,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 1,01</t>
+          <t>-19,24; -2,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 5,7</t>
+          <t>-11,15; 6,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 17,95</t>
+          <t>-13,1; 4,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,44; -2,11</t>
+          <t>-17,56; 0,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 3,43</t>
+          <t>-9,55; 3,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 8,65</t>
+          <t>-6,43; 9,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,81; -2,38</t>
+          <t>-14,17; -2,23</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-39,15%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65,47%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-25,39%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-53,95%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-80,97%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-39,15%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>65,47%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-83,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-93,23%</t>
+          <t>-93,8%</t>
         </is>
       </c>
     </row>
@@ -1215,29 +1215,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 396,04</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-60,97; 635,53</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 612,73</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-58,19; 617,53</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-86,79; 140,63</t>
+          <t>-85,5; 140,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,64; 290,45</t>
+          <t>-68,25; 369,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-4,17</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,94</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,18</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,47</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,27</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,97</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,11</t>
+          <t>-4,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,06</t>
+          <t>-8,53; 0,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -0,59</t>
+          <t>-7,33; 2,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,55; -1,1</t>
+          <t>-8,99; -0,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 0,74</t>
+          <t>-5,81; 2,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 2,51</t>
+          <t>-8,3; -0,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -0,19</t>
+          <t>-7,88; -0,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 0,56</t>
+          <t>-5,74; 0,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -0,34</t>
+          <t>-6,42; -0,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,02; -1,46</t>
+          <t>-6,93; -1,29</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-47,42%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-31,07%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-57,12%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-23,2%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-67,84%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-71,93%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-47,42%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-31,07%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-54,33%</t>
+          <t>-68,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-62,25%</t>
+          <t>-61,85%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 96,96</t>
+          <t>-80,6; 27,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-94,06; -2,0</t>
+          <t>-72,93; 53,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-93,9; -11,83</t>
+          <t>-83,75; 4,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-78,84; 33,05</t>
+          <t>-69,25; 90,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,23; 62,77</t>
+          <t>-93,58; -1,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,52; 4,41</t>
+          <t>-93,91; 7,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-67,81; 10,85</t>
+          <t>-65,66; 5,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,73; -3,51</t>
+          <t>-76,52; -3,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,46; -25,8</t>
+          <t>-81,58; -22,08</t>
         </is>
       </c>
     </row>
